--- a/01_data_model/01_code_lists/03_country_codes/input/countrycat2.xlsx
+++ b/01_data_model/01_code_lists/03_country_codes/input/countrycat2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vanniejo\Documents_local\01_dataplatform\002_DataModel\00_Code\04_codelists_countries\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vanniejo\Documents_local\01_dataplatform\021_SVbevraging\01_code\01_data_model\01_code_lists\03_country_codes\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AFCC9A8-7225-4492-B146-6EB0F0259D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2705B9E-3422-489F-A594-9ADCF56E812D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="50">
   <si>
     <t>valuen</t>
   </si>
@@ -158,6 +158,18 @@
   </si>
   <si>
     <t>notEU27</t>
+  </si>
+  <si>
+    <t>Onbekend</t>
+  </si>
+  <si>
+    <t>Inconnu</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>unknown</t>
   </si>
 </sst>
 </file>
@@ -510,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -740,6 +752,26 @@
         <v>45</v>
       </c>
     </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>99</v>
+      </c>
+      <c r="B12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
